--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486507_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486507_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4075</v>
+        <v>3.1957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6335</v>
+        <v>1.3293</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7739</v>
+        <v>1.8664</v>
       </c>
       <c r="G2" t="n">
         <v>-2.2894</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7158</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9349</v>
+        <v>-0.2391</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2191</v>
+        <v>0.3115</v>
       </c>
       <c r="V2" t="n">
         <v>3.0202</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0646</v>
+        <v>1.7706</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0142</v>
+        <v>0.1389</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0788</v>
+        <v>1.6318</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.857</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8028</v>
+        <v>-1.4204</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0542</v>
+        <v>1.3451</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1668</v>
+        <v>-0.1317</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0611</v>
+        <v>-0.6871</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2279</v>
+        <v>0.5554</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6902</v>
+        <v>0.0564</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8639</v>
+        <v>-0.7333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1737</v>
+        <v>0.7897</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1816</v>
+        <v>-0.024</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1526</v>
+        <v>-0.2944</v>
       </c>
       <c r="U3" t="n">
-        <v>0.029</v>
+        <v>0.2704</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8719</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4452</v>
+        <v>-0.2377</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3852</v>
+        <v>1.1096</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.857</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4204</v>
+        <v>-0.8028</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3451</v>
+        <v>-0.0542</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1317</v>
+        <v>-0.1668</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6871</v>
+        <v>0.0611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5554</v>
+        <v>-0.2279</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0564</v>
+        <v>-0.6902</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7333</v>
+        <v>-0.8639</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7897</v>
+        <v>0.1737</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8546</v>
+        <v>-0.0111</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8784</v>
+        <v>-0.0709</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0238</v>
+        <v>0.0598</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6914</v>
+        <v>0.8022</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4733</v>
+        <v>1.43</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7819</v>
+        <v>-0.6278</v>
       </c>
       <c r="G5" t="n">
         <v>1.172</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3443</v>
+        <v>0.4551</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0409</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2602</v>
+        <v>0.4143</v>
       </c>
       <c r="V5" t="n">
         <v>-1.695</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0054</v>
+        <v>0.1287</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4289</v>
+        <v>-0.8016</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4235</v>
+        <v>0.9303</v>
       </c>
       <c r="G6" t="n">
         <v>0.7501</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2759</v>
+        <v>-0.1418</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2209</v>
+        <v>-0.5936</v>
       </c>
       <c r="U6" t="n">
-        <v>0.945</v>
+        <v>0.4518</v>
       </c>
       <c r="V6" t="n">
         <v>0.3904</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0281</v>
+        <v>-0.092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2372</v>
+        <v>-0.4556</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2653</v>
+        <v>0.3636</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8568</v>
+        <v>0.8707</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8209</v>
+        <v>-1.3016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0359</v>
+        <v>2.1722</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6949</v>
+        <v>1.7642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5419</v>
+        <v>-0.1698</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>1.934</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5517</v>
+        <v>-0.8935</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3628</v>
+        <v>-1.1318</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1889</v>
+        <v>0.2382</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>-3.2626</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>1.896</v>
+        <v>-0.0703</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4372</v>
+        <v>-0.2824</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4588</v>
+        <v>0.2121</v>
       </c>
       <c r="V7" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.3252</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.4552</v>
       </c>
       <c r="X7" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1673</v>
+        <v>-0.525</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5926</v>
+        <v>-0.0491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4253</v>
+        <v>-0.4759</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8707</v>
+        <v>0.7982</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3016</v>
+        <v>0.6508</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1722</v>
+        <v>0.1474</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7642</v>
+        <v>1.0055</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1698</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.934</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8935</v>
+        <v>-0.2073</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1318</v>
+        <v>-0.3164</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2382</v>
+        <v>0.1091</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1456</v>
+        <v>-0.1709</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4194</v>
+        <v>-0.1622</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2737</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.9347</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.1952</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.3252</v>
       </c>
       <c r="X8" t="n">
         <v>-1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4895</v>
+        <v>-1.3191</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2293</v>
+        <v>-0.9922</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2602</v>
+        <v>-0.327</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7982</v>
+        <v>-0.8568</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6508</v>
+        <v>-0.8209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1474</v>
+        <v>-0.0359</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0055</v>
+        <v>0.6949</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.5419</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0382</v>
+        <v>0.153</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2073</v>
+        <v>-1.5517</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3164</v>
+        <v>-1.3628</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1091</v>
+        <v>-0.1889</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1354</v>
+        <v>0.6051</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>0.2079</v>
       </c>
       <c r="U9" t="n">
-        <v>0.207</v>
+        <v>0.3972</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9347</v>
+        <v>1.3252</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>2.4552</v>
       </c>
       <c r="X9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6696</v>
+        <v>-1.5191</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4986</v>
+        <v>-0.1865</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.171</v>
+        <v>-1.3326</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2586</v>
+        <v>0.2968</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5048</v>
+        <v>0.5383</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7634</v>
+        <v>-0.2415</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4794</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4412</v>
+        <v>0.6387</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2208</v>
+        <v>-0.4184</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9459</v>
+        <v>-0.1004</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7251</v>
+        <v>-0.318</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0582</v>
+        <v>-0.4038</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1971</v>
+        <v>-0.1622</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2552</v>
+        <v>-0.2415</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.0647</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7542</v>
+        <v>-1.6397</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2983</v>
+        <v>-1.6536</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4559</v>
+        <v>0.0139</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2968</v>
+        <v>0.2586</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5383</v>
+        <v>-0.5048</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2415</v>
+        <v>0.7634</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.4794</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6387</v>
+        <v>0.4412</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0765</v>
+        <v>0.0382</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4184</v>
+        <v>-0.2208</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1004</v>
+        <v>-0.9459</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.318</v>
+        <v>0.7251</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6388</v>
+        <v>-0.0282</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.274</v>
+        <v>0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3648</v>
+        <v>-0.0703</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0647</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9894000000000007</v>
+        <v>1.6742</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1631</v>
+        <v>-1.4781</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1524</v>
+        <v>3.1523</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0679000000000004</v>
+        <v>0.06789999999999996</v>
       </c>
       <c r="H12" t="n">
         <v>-4.3028</v>
@@ -1363,10 +1363,10 @@
         <v>4.3706</v>
       </c>
       <c r="J12" t="n">
-        <v>6.9623</v>
+        <v>6.962300000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.428199999999999</v>
+        <v>4.4282</v>
       </c>
       <c r="L12" t="n">
         <v>2.533999999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-6.8945</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.731</v>
+        <v>-8.730999999999998</v>
       </c>
       <c r="O12" t="n">
         <v>1.8364</v>
@@ -1390,10 +1390,10 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4024000000000003</v>
+        <v>0.2824999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1991</v>
+        <v>-1.5139</v>
       </c>
       <c r="U12" t="n">
         <v>1.7966</v>
@@ -1405,7 +1405,7 @@
         <v>7.2117</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.9752</v>
+        <v>-6.975199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4886</v>
+        <v>5.3473</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1142</v>
+        <v>2.8907</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3744</v>
+        <v>2.4567</v>
       </c>
       <c r="G13" t="n">
         <v>5.5011</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3801</v>
+        <v>0.2388</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1334</v>
+        <v>-0.3569</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5135</v>
+        <v>0.5957</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8532</v>
+        <v>5.0062</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5339</v>
+        <v>4.0926</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3194</v>
+        <v>0.9135</v>
       </c>
       <c r="G14" t="n">
         <v>2.5982</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4725</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7294</v>
+        <v>-0.1706</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2019</v>
+        <v>0.7961</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6365</v>
+        <v>3.4714</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4995</v>
+        <v>1.723</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1371</v>
+        <v>1.7485</v>
       </c>
       <c r="G15" t="n">
         <v>1.1687</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0.1277</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2584</v>
+        <v>-0.0348</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4488</v>
+        <v>0.1625</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3919</v>
+        <v>2.0534</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3515</v>
+        <v>2.4633</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9596</v>
+        <v>-0.4099</v>
       </c>
       <c r="G16" t="n">
         <v>2.5156</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7964</v>
+        <v>-0.1349</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3184</v>
+        <v>-0.2067</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4779</v>
+        <v>0.0718</v>
       </c>
       <c r="V16" t="n">
         <v>0.7602</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0493</v>
+        <v>-1.727</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4411</v>
+        <v>-1.5057</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6082</v>
+        <v>-0.2213</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7385</v>
+        <v>-0.6878</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3167</v>
+        <v>-1.4871</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.0552</v>
+        <v>0.7992</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4673</v>
+        <v>-0.2559</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5694</v>
+        <v>-0.9061</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.0368</v>
+        <v>0.6502</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2712</v>
+        <v>-0.432</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2528</v>
+        <v>-0.581</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0184</v>
+        <v>0.149</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6648</v>
+        <v>0.0261</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0263</v>
+        <v>-0.1622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.1884</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7156</v>
+        <v>-0.1952</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7156</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7462</v>
+        <v>-2.0538</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6174</v>
+        <v>-1.5587</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1288</v>
+        <v>-0.4951</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6878</v>
+        <v>-2.7385</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4871</v>
+        <v>1.3167</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7992</v>
+        <v>-4.0552</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2559</v>
+        <v>-1.4673</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9061</v>
+        <v>1.5694</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6502</v>
+        <v>-3.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.432</v>
+        <v>-1.2712</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.581</v>
+        <v>-0.2528</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>-1.0184</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0068</v>
+        <v>0.6603</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2808</v>
+        <v>0.7516</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-1.7156</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4435</v>
+        <v>-2.1942</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8554</v>
+        <v>-2.6319</v>
       </c>
       <c r="F19" t="n">
-        <v>0.412</v>
+        <v>0.4377</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0632</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3802</v>
+        <v>-0.131</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6044</v>
+        <v>-0.3809</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2242</v>
+        <v>0.2499</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1243</v>
+        <v>-2.2868</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7928</v>
+        <v>-3.3458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6685</v>
+        <v>1.059</v>
       </c>
       <c r="G20" t="n">
         <v>0.0766</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0259</v>
+        <v>-0.1884</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2089</v>
+        <v>-0.7619</v>
       </c>
       <c r="U20" t="n">
-        <v>0.183</v>
+        <v>0.5735</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3769</v>
+        <v>-3.4036</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.978</v>
+        <v>-3.9666</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3989</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4955</v>
+        <v>-3.9429</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8365</v>
+        <v>-2.9683</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6591</v>
+        <v>-0.9745</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3806</v>
+        <v>-2.0931</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1095</v>
+        <v>-1.9035</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4901</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1149</v>
+        <v>-1.8497</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9459</v>
+        <v>-1.0648</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1689</v>
+        <v>-0.7849</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>0.596</v>
+        <v>0.4077</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4026</v>
+        <v>0.3016</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1935</v>
+        <v>0.106</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.695</v>
+        <v>0.3491</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6194</v>
+        <v>-3.7122</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9666</v>
+        <v>-1.3133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3472</v>
+        <v>-2.3989</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9429</v>
+        <v>-2.4955</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9683</v>
+        <v>-0.8365</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9745</v>
+        <v>-1.6591</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0931</v>
+        <v>-1.3806</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9035</v>
+        <v>0.1095</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1896</v>
+        <v>-1.4901</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8497</v>
+        <v>-1.1149</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0648</v>
+        <v>-0.9459</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7849</v>
+        <v>-0.1689</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1919</v>
+        <v>0.2608</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3016</v>
+        <v>0.0673</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1097</v>
+        <v>0.1935</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3491</v>
+        <v>-1.695</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3491</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9894000000000003</v>
+        <v>0.5006999999999984</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.152200000000001</v>
+        <v>-3.152400000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1631</v>
+        <v>3.6532</v>
       </c>
       <c r="G23" t="n">
         <v>-0.06770000000000032</v>
@@ -2221,7 +2221,7 @@
         <v>-4.370700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>6.894600000000002</v>
+        <v>6.894600000000001</v>
       </c>
       <c r="K23" t="n">
         <v>8.730900000000002</v>
@@ -2248,16 +2248,16 @@
         <v>14.1381</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4024</v>
+        <v>1.8926</v>
       </c>
       <c r="T23" t="n">
         <v>-1.7964</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1991</v>
+        <v>3.689</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2365000000000001</v>
+        <v>-0.2365000000000002</v>
       </c>
       <c r="W23" t="n">
         <v>6.975</v>
